--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I531"/>
+  <dimension ref="A1:I533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17810,7 +17810,7 @@
         <v>418.21</v>
       </c>
       <c r="D531" t="n">
-        <v>339.3</v>
+        <v>347.48</v>
       </c>
       <c r="E531" t="n">
         <v>361.67</v>
@@ -17825,6 +17825,72 @@
         <v>378.77</v>
       </c>
       <c r="I531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>407.78</v>
+      </c>
+      <c r="C532" t="n">
+        <v>425.98</v>
+      </c>
+      <c r="D532" t="n">
+        <v>359.6</v>
+      </c>
+      <c r="E532" t="n">
+        <v>364.19</v>
+      </c>
+      <c r="F532" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="G532" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="H532" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>418.11</v>
+      </c>
+      <c r="C533" t="n">
+        <v>436.05</v>
+      </c>
+      <c r="D533" t="n">
+        <v>369.19</v>
+      </c>
+      <c r="E533" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="F533" t="n">
+        <v>359.21</v>
+      </c>
+      <c r="G533" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="H533" t="n">
+        <v>382.63</v>
+      </c>
+      <c r="I533" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17841,7 +17907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B559"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23434,6 +23500,26 @@
       </c>
       <c r="B559" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -23602,28 +23688,28 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.036216383543285</v>
+        <v>-4.04246796168897</v>
       </c>
       <c r="J2" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K2" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2958419160095336</v>
+        <v>0.2982371188820365</v>
       </c>
       <c r="M2" t="n">
-        <v>36.25345046447632</v>
+        <v>36.13636125861522</v>
       </c>
       <c r="N2" t="n">
-        <v>2000.210853982716</v>
+        <v>1992.692607286257</v>
       </c>
       <c r="O2" t="n">
-        <v>44.72371690705856</v>
+        <v>44.63958565316504</v>
       </c>
       <c r="P2" t="n">
-        <v>526.8363752444156</v>
+        <v>526.9039522828336</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -23684,28 +23770,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.900165912228511</v>
+        <v>-4.883798241019291</v>
       </c>
       <c r="J3" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3915138877610304</v>
+        <v>0.391754641537291</v>
       </c>
       <c r="M3" t="n">
-        <v>35.26131661131347</v>
+        <v>35.21501991075527</v>
       </c>
       <c r="N3" t="n">
-        <v>1897.974876407342</v>
+        <v>1892.085369035992</v>
       </c>
       <c r="O3" t="n">
-        <v>43.56575348145997</v>
+        <v>43.49810764890803</v>
       </c>
       <c r="P3" t="n">
-        <v>539.7589654755083</v>
+        <v>539.579763118221</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -23766,28 +23852,28 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5878833699360977</v>
+        <v>-0.6071590999215946</v>
       </c>
       <c r="J4" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K4" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03244458823893992</v>
+        <v>0.03471725954984839</v>
       </c>
       <c r="M4" t="n">
-        <v>18.38400191253274</v>
+        <v>18.39184984677626</v>
       </c>
       <c r="N4" t="n">
-        <v>536.1768381589278</v>
+        <v>535.7737853740671</v>
       </c>
       <c r="O4" t="n">
-        <v>23.15549261317772</v>
+        <v>23.146787798182</v>
       </c>
       <c r="P4" t="n">
-        <v>408.4899204618893</v>
+        <v>408.6948103886851</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -23848,28 +23934,28 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5484910323561695</v>
+        <v>-0.5533812892394897</v>
       </c>
       <c r="J5" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K5" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07369402674985726</v>
+        <v>0.07544620055376161</v>
       </c>
       <c r="M5" t="n">
-        <v>11.46857345406629</v>
+        <v>11.44862667255005</v>
       </c>
       <c r="N5" t="n">
-        <v>200.7111629862258</v>
+        <v>200.125310690412</v>
       </c>
       <c r="O5" t="n">
-        <v>14.16725672055906</v>
+        <v>14.14656533192464</v>
       </c>
       <c r="P5" t="n">
-        <v>387.2849885246852</v>
+        <v>387.3362443154102</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -23930,28 +24016,28 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3996864541950582</v>
+        <v>-0.4055311601946104</v>
       </c>
       <c r="J6" t="n">
+        <v>532</v>
+      </c>
+      <c r="K6" t="n">
         <v>530</v>
       </c>
-      <c r="K6" t="n">
-        <v>528</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.06267748872522338</v>
+        <v>0.0648142311787665</v>
       </c>
       <c r="M6" t="n">
-        <v>9.243480641518831</v>
+        <v>9.231983599319834</v>
       </c>
       <c r="N6" t="n">
-        <v>127.0244392822855</v>
+        <v>126.762207116584</v>
       </c>
       <c r="O6" t="n">
-        <v>11.27051193523548</v>
+        <v>11.25887237322566</v>
       </c>
       <c r="P6" t="n">
-        <v>376.4176765897566</v>
+        <v>376.4788996879074</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24012,28 +24098,28 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06910631060489845</v>
+        <v>-0.07752635687361616</v>
       </c>
       <c r="J7" t="n">
+        <v>532</v>
+      </c>
+      <c r="K7" t="n">
         <v>530</v>
       </c>
-      <c r="K7" t="n">
-        <v>528</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.002398381283443052</v>
+        <v>0.003029312762966474</v>
       </c>
       <c r="M7" t="n">
-        <v>8.721676328015635</v>
+        <v>8.726980695181391</v>
       </c>
       <c r="N7" t="n">
-        <v>105.6197904060151</v>
+        <v>105.6697897777732</v>
       </c>
       <c r="O7" t="n">
-        <v>10.27714894345777</v>
+        <v>10.27958120634169</v>
       </c>
       <c r="P7" t="n">
-        <v>373.9871723872062</v>
+        <v>374.0753721974268</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24094,28 +24180,28 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04691794687972987</v>
+        <v>0.0428201762293523</v>
       </c>
       <c r="J8" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K8" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004025595849837305</v>
+        <v>0.003371248628800561</v>
       </c>
       <c r="M8" t="n">
-        <v>3.903164250592674</v>
+        <v>3.90973366825336</v>
       </c>
       <c r="N8" t="n">
-        <v>28.97449426638954</v>
+        <v>28.972768293696</v>
       </c>
       <c r="O8" t="n">
-        <v>5.382796138289981</v>
+        <v>5.382635812842626</v>
       </c>
       <c r="P8" t="n">
-        <v>385.7416242080236</v>
+        <v>385.7846358251061</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24157,7 +24243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I531"/>
+  <dimension ref="A1:I533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48812,7 +48898,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>-36.54464910123961,174.70912635598881</t>
+          <t>-36.54467199292907,174.7092132061059</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -48836,6 +48922,100 @@
         </is>
       </c>
       <c r="I531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-36.54339921657932,174.71028884831483</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-36.5441409283927,174.71028003693476</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-36.544705910570016,174.70934188876552</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-36.54538329656337,174.70903105901075</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-36.54601600632815,174.70858773502536</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-36.54669487699104,174.70829754098975</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-36.54742571951162,174.70844892136523</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-36.54341951572633,174.71040145123874</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-36.544161258007804,174.71038965470362</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-36.54473274794264,174.70944370952697</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-36.545399999855434,174.70907893738882</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-36.54602195142038,174.70860596066692</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-36.54669882019202,174.70832025433202</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-36.54742696682497,174.7084699757774</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I533"/>
+  <dimension ref="A1:I534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17810,7 +17810,7 @@
         <v>418.21</v>
       </c>
       <c r="D531" t="n">
-        <v>347.48</v>
+        <v>339.3</v>
       </c>
       <c r="E531" t="n">
         <v>361.67</v>
@@ -17837,13 +17837,13 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>407.78</v>
+        <v>392.92</v>
       </c>
       <c r="C532" t="n">
-        <v>425.98</v>
+        <v>412.67</v>
       </c>
       <c r="D532" t="n">
-        <v>359.6</v>
+        <v>339.3</v>
       </c>
       <c r="E532" t="n">
         <v>364.19</v>
@@ -17870,13 +17870,13 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>418.11</v>
+        <v>392.92</v>
       </c>
       <c r="C533" t="n">
-        <v>436.05</v>
+        <v>412.67</v>
       </c>
       <c r="D533" t="n">
-        <v>369.19</v>
+        <v>339.3</v>
       </c>
       <c r="E533" t="n">
         <v>368.86</v>
@@ -17891,6 +17891,39 @@
         <v>382.63</v>
       </c>
       <c r="I533" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>384.87</v>
+      </c>
+      <c r="C534" t="n">
+        <v>409.85</v>
+      </c>
+      <c r="D534" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="E534" t="n">
+        <v>369.19</v>
+      </c>
+      <c r="F534" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="G534" t="n">
+        <v>362.86</v>
+      </c>
+      <c r="H534" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="I534" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17907,7 +17940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B561"/>
+  <dimension ref="A1:B562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23520,6 +23553,16 @@
       </c>
       <c r="B561" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -23688,28 +23731,28 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.04246796168897</v>
+        <v>-4.072653004297492</v>
       </c>
       <c r="J2" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K2" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2982371188820365</v>
+        <v>0.3017283400298789</v>
       </c>
       <c r="M2" t="n">
-        <v>36.13636125861522</v>
+        <v>36.18718316172572</v>
       </c>
       <c r="N2" t="n">
-        <v>1992.692607286257</v>
+        <v>1993.85399855539</v>
       </c>
       <c r="O2" t="n">
-        <v>44.63958565316504</v>
+        <v>44.6525922937895</v>
       </c>
       <c r="P2" t="n">
-        <v>526.9039522828336</v>
+        <v>527.2308336213694</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -23770,28 +23813,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.883798241019291</v>
+        <v>-4.899056170159889</v>
       </c>
       <c r="J3" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K3" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L3" t="n">
-        <v>0.391754641537291</v>
+        <v>0.3944841281098617</v>
       </c>
       <c r="M3" t="n">
-        <v>35.21501991075527</v>
+        <v>35.05976107390558</v>
       </c>
       <c r="N3" t="n">
-        <v>1892.085369035992</v>
+        <v>1886.644879086321</v>
       </c>
       <c r="O3" t="n">
-        <v>43.49810764890803</v>
+        <v>43.43552554173048</v>
       </c>
       <c r="P3" t="n">
-        <v>539.579763118221</v>
+        <v>539.7468274050975</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -23852,28 +23895,28 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6071590999215946</v>
+        <v>-0.6481297333690172</v>
       </c>
       <c r="J4" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K4" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03471725954984839</v>
+        <v>0.03862205946256603</v>
       </c>
       <c r="M4" t="n">
-        <v>18.39184984677626</v>
+        <v>18.5247798735542</v>
       </c>
       <c r="N4" t="n">
-        <v>535.7737853740671</v>
+        <v>547.8955900540814</v>
       </c>
       <c r="O4" t="n">
-        <v>23.146787798182</v>
+        <v>23.40716962928413</v>
       </c>
       <c r="P4" t="n">
-        <v>408.6948103886851</v>
+        <v>409.1306385630459</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -23934,28 +23977,28 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5533812892394897</v>
+        <v>-0.5547539367287226</v>
       </c>
       <c r="J5" t="n">
+        <v>533</v>
+      </c>
+      <c r="K5" t="n">
         <v>532</v>
       </c>
-      <c r="K5" t="n">
-        <v>531</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07544620055376161</v>
+        <v>0.0760833680007067</v>
       </c>
       <c r="M5" t="n">
-        <v>11.44862667255005</v>
+        <v>11.43356764752484</v>
       </c>
       <c r="N5" t="n">
-        <v>200.125310690412</v>
+        <v>199.7727140588389</v>
       </c>
       <c r="O5" t="n">
-        <v>14.14656533192464</v>
+        <v>14.13409756789725</v>
       </c>
       <c r="P5" t="n">
-        <v>387.3362443154102</v>
+        <v>387.3506858106888</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24016,28 +24059,28 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4055311601946104</v>
+        <v>-0.4079563581263406</v>
       </c>
       <c r="J6" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K6" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0648142311787665</v>
+        <v>0.06576637947969344</v>
       </c>
       <c r="M6" t="n">
-        <v>9.231983599319834</v>
+        <v>9.224268957582407</v>
       </c>
       <c r="N6" t="n">
-        <v>126.762207116584</v>
+        <v>126.5972553889727</v>
       </c>
       <c r="O6" t="n">
-        <v>11.25887237322566</v>
+        <v>11.2515445779223</v>
       </c>
       <c r="P6" t="n">
-        <v>376.4788996879074</v>
+        <v>376.5043996944303</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24098,28 +24141,28 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07752635687361616</v>
+        <v>-0.08107037211584046</v>
       </c>
       <c r="J7" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K7" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003029312762966474</v>
+        <v>0.003320814678120843</v>
       </c>
       <c r="M7" t="n">
-        <v>8.726980695181391</v>
+        <v>8.72645634091846</v>
       </c>
       <c r="N7" t="n">
-        <v>105.6697897777732</v>
+        <v>105.6283270126503</v>
       </c>
       <c r="O7" t="n">
-        <v>10.27958120634169</v>
+        <v>10.27756425485388</v>
       </c>
       <c r="P7" t="n">
-        <v>374.0753721974268</v>
+        <v>374.1126361298306</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24180,28 +24223,28 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0428201762293523</v>
+        <v>0.04093868168090998</v>
       </c>
       <c r="J8" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K8" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003371248628800561</v>
+        <v>0.003090790765432616</v>
       </c>
       <c r="M8" t="n">
-        <v>3.90973366825336</v>
+        <v>3.912237197054945</v>
       </c>
       <c r="N8" t="n">
-        <v>28.972768293696</v>
+        <v>28.96207098830639</v>
       </c>
       <c r="O8" t="n">
-        <v>5.382635812842626</v>
+        <v>5.381642034575171</v>
       </c>
       <c r="P8" t="n">
-        <v>385.7846358251061</v>
+        <v>385.8044599428377</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24243,7 +24286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I533"/>
+  <dimension ref="A1:I534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48898,7 +48941,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>-36.54467199292907,174.7092132061059</t>
+          <t>-36.54464910123961,174.70912635598881</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -48935,17 +48978,17 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>-36.54339921657932,174.71028884831483</t>
+          <t>-36.54337001548722,174.71012686588938</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>-36.5441409283927,174.71028003693476</t>
+          <t>-36.54411405761224,174.71013514997588</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>-36.544705910570016,174.70934188876552</t>
+          <t>-36.54464910123961,174.70912635598881</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -48982,17 +49025,17 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>-36.54341951572633,174.71040145123874</t>
+          <t>-36.54337001548722,174.71012686588938</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>-36.544161258007804,174.71038965470362</t>
+          <t>-36.54411405761224,174.71013514997588</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>-36.54473274794264,174.70944370952697</t>
+          <t>-36.54464910123961,174.70912635598881</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -49016,6 +49059,53 @@
         </is>
       </c>
       <c r="I533" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-36.54335419649813,174.7100391163725</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-36.54410836445623,174.71010445267578</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-36.54466841085967,174.7091996158643</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-36.54540118017297,174.70908232065827</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-36.54602296478809,174.70860906731062</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-36.54669990077999,174.70832647866177</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-36.54742659725104,174.708463737433</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I534"/>
+  <dimension ref="A1:I535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17924,6 +17924,39 @@
         <v>382.07</v>
       </c>
       <c r="I534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>386.08</v>
+      </c>
+      <c r="C535" t="n">
+        <v>409.4</v>
+      </c>
+      <c r="D535" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="E535" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="F535" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="G535" t="n">
+        <v>365.67</v>
+      </c>
+      <c r="H535" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="I535" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17940,7 +17973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B562"/>
+  <dimension ref="A1:B563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23563,6 +23596,16 @@
       </c>
       <c r="B562" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -23731,34 +23774,30 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.072653004297492</v>
+        <v>-4.086090210212496</v>
       </c>
       <c r="J2" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K2" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3017283400298789</v>
+        <v>0.3038027601473905</v>
       </c>
       <c r="M2" t="n">
-        <v>36.18718316172572</v>
+        <v>36.16968585202231</v>
       </c>
       <c r="N2" t="n">
-        <v>1993.85399855539</v>
+        <v>1992.119771198853</v>
       </c>
       <c r="O2" t="n">
-        <v>44.6525922937895</v>
+        <v>44.63316895761327</v>
       </c>
       <c r="P2" t="n">
-        <v>527.2308336213694</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>527.377175213207</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.70584385628675 -36.54259781509065, 174.71588991377357 -36.54440878858775)</t>
@@ -23813,34 +23852,30 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.899056170159889</v>
+        <v>-4.899348964734247</v>
       </c>
       <c r="J3" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3944841281098617</v>
+        <v>0.3955527150104811</v>
       </c>
       <c r="M3" t="n">
-        <v>35.05976107390558</v>
+        <v>34.99120892085383</v>
       </c>
       <c r="N3" t="n">
-        <v>1886.644879086321</v>
+        <v>1882.895102917329</v>
       </c>
       <c r="O3" t="n">
-        <v>43.43552554173048</v>
+        <v>43.39233921923695</v>
       </c>
       <c r="P3" t="n">
-        <v>539.7468274050975</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>539.7500569238022</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.7056430475756 -36.543280853540374, 174.7156752039462 -36.54514137803523)</t>
@@ -23895,34 +23930,30 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6481297333690172</v>
+        <v>-0.6659261044730422</v>
       </c>
       <c r="J4" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K4" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03862205946256603</v>
+        <v>0.04058170396190242</v>
       </c>
       <c r="M4" t="n">
-        <v>18.5247798735542</v>
+        <v>18.56361281182547</v>
       </c>
       <c r="N4" t="n">
-        <v>547.8955900540814</v>
+        <v>550.6925675122344</v>
       </c>
       <c r="O4" t="n">
-        <v>23.40716962928413</v>
+        <v>23.46683974275689</v>
       </c>
       <c r="P4" t="n">
-        <v>409.1306385630459</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>409.3210723072191</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.70552392422738 -36.54369951485913, 174.71530823912116 -36.54627830930548)</t>
@@ -23977,34 +24008,30 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5547539367287226</v>
+        <v>-0.5531447764229492</v>
       </c>
       <c r="J5" t="n">
+        <v>534</v>
+      </c>
+      <c r="K5" t="n">
         <v>533</v>
       </c>
-      <c r="K5" t="n">
-        <v>532</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0760833680007067</v>
+        <v>0.07596568465804132</v>
       </c>
       <c r="M5" t="n">
-        <v>11.43356764752484</v>
+        <v>11.4201200574372</v>
       </c>
       <c r="N5" t="n">
-        <v>199.7727140588389</v>
+        <v>199.4301342701065</v>
       </c>
       <c r="O5" t="n">
-        <v>14.13409756789725</v>
+        <v>14.12197345522596</v>
       </c>
       <c r="P5" t="n">
-        <v>387.3506858106888</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>387.3336940596786</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.70529732473383 -36.544080629117914, 174.7147443266875 -36.54737629062078)</t>
@@ -24059,34 +24086,30 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4079563581263406</v>
+        <v>-0.4095629276283688</v>
       </c>
       <c r="J6" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K6" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06576637947969344</v>
+        <v>0.06650129536776195</v>
       </c>
       <c r="M6" t="n">
-        <v>9.224268957582407</v>
+        <v>9.213266149567493</v>
       </c>
       <c r="N6" t="n">
-        <v>126.5972553889727</v>
+        <v>126.3914885652658</v>
       </c>
       <c r="O6" t="n">
-        <v>11.2515445779223</v>
+        <v>11.2423969225991</v>
       </c>
       <c r="P6" t="n">
-        <v>376.5043996944303</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>376.5213541211018</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.70488622530033 -36.54480851896808, 174.71442849596295 -36.547921034862135)</t>
@@ -24141,34 +24164,30 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08107037211584046</v>
+        <v>-0.08350648365247</v>
       </c>
       <c r="J7" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K7" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003320814678120843</v>
+        <v>0.003535306736397903</v>
       </c>
       <c r="M7" t="n">
-        <v>8.72645634091846</v>
+        <v>8.720872989660856</v>
       </c>
       <c r="N7" t="n">
-        <v>105.6283270126503</v>
+        <v>105.5038101961549</v>
       </c>
       <c r="O7" t="n">
-        <v>10.27756425485388</v>
+        <v>10.27150476785923</v>
       </c>
       <c r="P7" t="n">
-        <v>374.1126361298306</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>374.1383448678338</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.70436412473794 -36.546011935554034, 174.71442789145658 -36.54775897743813)</t>
@@ -24223,34 +24242,30 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04093868168090998</v>
+        <v>0.03973744369602238</v>
       </c>
       <c r="J8" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K8" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003090790765432616</v>
+        <v>0.002923283914506136</v>
       </c>
       <c r="M8" t="n">
-        <v>3.912237197054945</v>
+        <v>3.911144843522975</v>
       </c>
       <c r="N8" t="n">
-        <v>28.96207098830639</v>
+        <v>28.92510715276176</v>
       </c>
       <c r="O8" t="n">
-        <v>5.381642034575171</v>
+        <v>5.378206685574826</v>
       </c>
       <c r="P8" t="n">
-        <v>385.8044599428377</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>385.8171633646394</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.7042075263798 -36.54717437235482, 174.71447462774003 -36.54778254285024)</t>
@@ -24286,7 +24301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I534"/>
+  <dimension ref="A1:I535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49111,6 +49126,53 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-36.543356574263406,174.7100523060493</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-36.54410745597315,174.71009955417085</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-36.54466995003031,174.70920545542108</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-36.545428506284544,174.70916064849993</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-36.54602988946518,174.70863029604482</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-36.54670522788424,174.70835716351783</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-36.54742773896946,174.7084830094614</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I535"/>
+  <dimension ref="A1:I536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17957,6 +17957,39 @@
         <v>383.8</v>
       </c>
       <c r="I535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>386.08</v>
+      </c>
+      <c r="C536" t="n">
+        <v>404.59</v>
+      </c>
+      <c r="D536" t="n">
+        <v>353.44</v>
+      </c>
+      <c r="E536" t="n">
+        <v>375.56</v>
+      </c>
+      <c r="F536" t="n">
+        <v>361.53</v>
+      </c>
+      <c r="G536" t="n">
+        <v>365.84</v>
+      </c>
+      <c r="H536" t="n">
+        <v>383.38</v>
+      </c>
+      <c r="I536" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17973,7 +18006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B563"/>
+  <dimension ref="A1:B564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23606,6 +23639,16 @@
       </c>
       <c r="B563" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -23774,28 +23817,28 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.086090210212496</v>
+        <v>-4.099352217562873</v>
       </c>
       <c r="J2" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3038027601473905</v>
+        <v>0.3058623914096619</v>
       </c>
       <c r="M2" t="n">
-        <v>36.16968585202231</v>
+        <v>36.15181100708607</v>
       </c>
       <c r="N2" t="n">
-        <v>1992.119771198853</v>
+        <v>1990.35526556896</v>
       </c>
       <c r="O2" t="n">
-        <v>44.63316895761327</v>
+        <v>44.61339782586572</v>
       </c>
       <c r="P2" t="n">
-        <v>527.377175213207</v>
+        <v>527.5217239588071</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23852,28 +23895,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.899348964734247</v>
+        <v>-4.901560808778667</v>
       </c>
       <c r="J3" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3955527150104811</v>
+        <v>0.3967976013991381</v>
       </c>
       <c r="M3" t="n">
-        <v>34.99120892085383</v>
+        <v>34.9304274955164</v>
       </c>
       <c r="N3" t="n">
-        <v>1882.895102917329</v>
+        <v>1879.217180948927</v>
       </c>
       <c r="O3" t="n">
-        <v>43.39233921923695</v>
+        <v>43.34993864988654</v>
       </c>
       <c r="P3" t="n">
-        <v>539.7500569238022</v>
+        <v>539.7744729304235</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23930,28 +23973,28 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6659261044730422</v>
+        <v>-0.6809070066319787</v>
       </c>
       <c r="J4" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K4" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04058170396190242</v>
+        <v>0.04232385196073096</v>
       </c>
       <c r="M4" t="n">
-        <v>18.56361281182547</v>
+        <v>18.59103562720537</v>
       </c>
       <c r="N4" t="n">
-        <v>550.6925675122344</v>
+        <v>552.3897757088288</v>
       </c>
       <c r="O4" t="n">
-        <v>23.46683974275689</v>
+        <v>23.50297376309706</v>
       </c>
       <c r="P4" t="n">
-        <v>409.3210723072191</v>
+        <v>409.4815035459267</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24008,28 +24051,28 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5531447764229492</v>
+        <v>-0.5520382959595614</v>
       </c>
       <c r="J5" t="n">
+        <v>535</v>
+      </c>
+      <c r="K5" t="n">
         <v>534</v>
       </c>
-      <c r="K5" t="n">
-        <v>533</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07596568465804132</v>
+        <v>0.0759793508405181</v>
       </c>
       <c r="M5" t="n">
-        <v>11.4201200574372</v>
+        <v>11.40421768984016</v>
       </c>
       <c r="N5" t="n">
-        <v>199.4301342701065</v>
+        <v>199.0720143695031</v>
       </c>
       <c r="O5" t="n">
-        <v>14.12197345522596</v>
+        <v>14.10928823043541</v>
       </c>
       <c r="P5" t="n">
-        <v>387.3336940596786</v>
+        <v>387.3220010189219</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24086,28 +24129,28 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4095629276283688</v>
+        <v>-0.4111594736885939</v>
       </c>
       <c r="J6" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K6" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06650129536776195</v>
+        <v>0.06723767682667425</v>
       </c>
       <c r="M6" t="n">
-        <v>9.213266149567493</v>
+        <v>9.202252475861926</v>
       </c>
       <c r="N6" t="n">
-        <v>126.3914885652658</v>
+        <v>126.186376585651</v>
       </c>
       <c r="O6" t="n">
-        <v>11.2423969225991</v>
+        <v>11.23327096555812</v>
       </c>
       <c r="P6" t="n">
-        <v>376.5213541211018</v>
+        <v>376.5382161944185</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24164,28 +24207,28 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08350648365247</v>
+        <v>-0.08585320635271786</v>
       </c>
       <c r="J7" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K7" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003535306736397903</v>
+        <v>0.003749534577752622</v>
       </c>
       <c r="M7" t="n">
-        <v>8.720872989660856</v>
+        <v>8.714894106046044</v>
       </c>
       <c r="N7" t="n">
-        <v>105.5038101961549</v>
+        <v>105.375047644045</v>
       </c>
       <c r="O7" t="n">
-        <v>10.27150476785923</v>
+        <v>10.26523490447467</v>
       </c>
       <c r="P7" t="n">
-        <v>374.1383448678338</v>
+        <v>374.1631300032027</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24242,28 +24285,28 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03973744369602238</v>
+        <v>0.038385657195331</v>
       </c>
       <c r="J8" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K8" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002923283914506136</v>
+        <v>0.002737806823186473</v>
       </c>
       <c r="M8" t="n">
-        <v>3.911144843522975</v>
+        <v>3.910836924306204</v>
       </c>
       <c r="N8" t="n">
-        <v>28.92510715276176</v>
+        <v>28.89326994093012</v>
       </c>
       <c r="O8" t="n">
-        <v>5.378206685574826</v>
+        <v>5.37524603538574</v>
       </c>
       <c r="P8" t="n">
-        <v>385.8171633646394</v>
+        <v>385.831470343017</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24301,7 +24344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I535"/>
+  <dimension ref="A1:I536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49173,6 +49216,53 @@
         </is>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-36.543356574263406,174.7100523060493</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-36.544097745285605,174.71004719460248</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-36.54468867191876,174.70927648568414</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-36.54542396385868,174.70914762803037</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-36.546029788128486,174.70862998538036</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-36.54670555016431,174.70835901989713</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-36.54742746178956,174.70847833070303</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I536"/>
+  <dimension ref="A1:I539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17992,6 +17992,105 @@
       <c r="I536" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>375.65</v>
+      </c>
+      <c r="C537" t="n">
+        <v>400.89</v>
+      </c>
+      <c r="D537" t="n">
+        <v>353.44</v>
+      </c>
+      <c r="E537" t="n">
+        <v>375.11</v>
+      </c>
+      <c r="F537" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="G537" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="H537" t="n">
+        <v>383.02</v>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>398.54</v>
+      </c>
+      <c r="C538" t="n">
+        <v>400.89</v>
+      </c>
+      <c r="D538" t="n">
+        <v>353.44</v>
+      </c>
+      <c r="E538" t="n">
+        <v>378.13</v>
+      </c>
+      <c r="F538" t="n">
+        <v>362.87</v>
+      </c>
+      <c r="G538" t="n">
+        <v>368.16</v>
+      </c>
+      <c r="H538" t="n">
+        <v>384.95</v>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>398.54</v>
+      </c>
+      <c r="C539" t="n">
+        <v>353.13</v>
+      </c>
+      <c r="D539" t="n">
+        <v>341.33</v>
+      </c>
+      <c r="E539" t="n">
+        <v>378.13</v>
+      </c>
+      <c r="F539" t="n">
+        <v>363.73</v>
+      </c>
+      <c r="G539" t="n">
+        <v>369.74</v>
+      </c>
+      <c r="H539" t="n">
+        <v>388.75</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B564"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23649,6 +23748,36 @@
       </c>
       <c r="B564" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -23817,28 +23946,28 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.099352217562873</v>
+        <v>-4.132232600744036</v>
       </c>
       <c r="J2" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3058623914096619</v>
+        <v>0.31149250800311</v>
       </c>
       <c r="M2" t="n">
-        <v>36.15181100708607</v>
+        <v>36.07024411946238</v>
       </c>
       <c r="N2" t="n">
-        <v>1990.35526556896</v>
+        <v>1983.8169531713</v>
       </c>
       <c r="O2" t="n">
-        <v>44.61339782586572</v>
+        <v>44.54006009393454</v>
       </c>
       <c r="P2" t="n">
-        <v>527.5217239588071</v>
+        <v>527.8814851374201</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23895,28 +24024,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.901560808778667</v>
+        <v>-4.9313537107946</v>
       </c>
       <c r="J3" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K3" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3967976013991381</v>
+        <v>0.4020058288043963</v>
       </c>
       <c r="M3" t="n">
-        <v>34.9304274955164</v>
+        <v>34.83778163451612</v>
       </c>
       <c r="N3" t="n">
-        <v>1879.217180948927</v>
+        <v>1874.535676195444</v>
       </c>
       <c r="O3" t="n">
-        <v>43.34993864988654</v>
+        <v>43.29590830777712</v>
       </c>
       <c r="P3" t="n">
-        <v>539.7744729304235</v>
+        <v>540.1051906335986</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23973,28 +24102,28 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6809070066319787</v>
+        <v>-0.729801392699493</v>
       </c>
       <c r="J4" t="n">
+        <v>538</v>
+      </c>
+      <c r="K4" t="n">
         <v>535</v>
       </c>
-      <c r="K4" t="n">
-        <v>532</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04232385196073096</v>
+        <v>0.04809390584138551</v>
       </c>
       <c r="M4" t="n">
-        <v>18.59103562720537</v>
+        <v>18.68862470787009</v>
       </c>
       <c r="N4" t="n">
-        <v>552.3897757088288</v>
+        <v>559.1713940089921</v>
       </c>
       <c r="O4" t="n">
-        <v>23.50297376309706</v>
+        <v>23.64680515437534</v>
       </c>
       <c r="P4" t="n">
-        <v>409.4815035459267</v>
+        <v>410.0074032580412</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24051,28 +24180,28 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5520382959595614</v>
+        <v>-0.5469075508896826</v>
       </c>
       <c r="J5" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K5" t="n">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0759793508405181</v>
+        <v>0.07552940859311885</v>
       </c>
       <c r="M5" t="n">
-        <v>11.40421768984016</v>
+        <v>11.36553805969884</v>
       </c>
       <c r="N5" t="n">
-        <v>199.0720143695031</v>
+        <v>198.0812531806938</v>
       </c>
       <c r="O5" t="n">
-        <v>14.10928823043541</v>
+        <v>14.07413418938067</v>
       </c>
       <c r="P5" t="n">
-        <v>387.3220010189219</v>
+        <v>387.2675320446643</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24129,28 +24258,28 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4111594736885939</v>
+        <v>-0.4146164813013873</v>
       </c>
       <c r="J6" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K6" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06723767682667425</v>
+        <v>0.06908898708794564</v>
       </c>
       <c r="M6" t="n">
-        <v>9.202252475861926</v>
+        <v>9.164150135030413</v>
       </c>
       <c r="N6" t="n">
-        <v>126.186376585651</v>
+        <v>125.53684033351</v>
       </c>
       <c r="O6" t="n">
-        <v>11.23327096555812</v>
+        <v>11.20432239510762</v>
       </c>
       <c r="P6" t="n">
-        <v>376.5382161944185</v>
+        <v>376.5748658232695</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24207,28 +24336,28 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08585320635271786</v>
+        <v>-0.09060578617067573</v>
       </c>
       <c r="J7" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K7" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003749534577752622</v>
+        <v>0.004223570232351537</v>
       </c>
       <c r="M7" t="n">
-        <v>8.714894106046044</v>
+        <v>8.687008927410167</v>
       </c>
       <c r="N7" t="n">
-        <v>105.375047644045</v>
+        <v>104.8993303297174</v>
       </c>
       <c r="O7" t="n">
-        <v>10.26523490447467</v>
+        <v>10.24203741106805</v>
       </c>
       <c r="P7" t="n">
-        <v>374.1631300032027</v>
+        <v>374.2135086062279</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24285,28 +24414,28 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.038385657195331</v>
+        <v>0.03692426811648174</v>
       </c>
       <c r="J8" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K8" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002737806823186473</v>
+        <v>0.00256291573747236</v>
       </c>
       <c r="M8" t="n">
-        <v>3.910836924306204</v>
+        <v>3.903565886777204</v>
       </c>
       <c r="N8" t="n">
-        <v>28.89326994093012</v>
+        <v>28.77096776474988</v>
       </c>
       <c r="O8" t="n">
-        <v>5.37524603538574</v>
+        <v>5.363857545158137</v>
       </c>
       <c r="P8" t="n">
-        <v>385.831470343017</v>
+        <v>385.8469598537134</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24344,7 +24473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I536"/>
+  <dimension ref="A1:I539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49263,6 +49392,147 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-36.54333607827102,174.70993861324007</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-36.54409027551008,174.71000691801973</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-36.54468867191876,174.70927648568414</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-36.54542235433736,174.70914301447854</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-36.546028538308995,174.70862615385246</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-36.546704469578074,174.70835279556653</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-36.54742722420663,174.70847432033872</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-36.54338105926434,174.71018812706254</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-36.54409027551008,174.71000691801973</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-36.54468867191876,174.70927648568414</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-36.545433156010304,174.7091739765411</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-36.54603431450073,174.70864386172562</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-36.546709948336485,174.7083843540163</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-36.547428497913494,174.70849582034757</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-36.54338105926434,174.71018812706254</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-36.54399385359909,174.7094870241851</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-36.54465478219059,174.70914790925292</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-36.545433156010304,174.7091739765411</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-36.54603721948502,174.70865276744055</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-36.54671294364026,174.70840160742657</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-36.547431005718735,174.70853815197282</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I539"/>
+  <dimension ref="A1:I544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>398.54</v>
+        <v>375.65</v>
       </c>
       <c r="C538" t="n">
         <v>400.89</v>
@@ -18068,19 +18068,19 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>398.54</v>
+        <v>375.65</v>
       </c>
       <c r="C539" t="n">
-        <v>353.13</v>
+        <v>400.89</v>
       </c>
       <c r="D539" t="n">
-        <v>341.33</v>
+        <v>366.7</v>
       </c>
       <c r="E539" t="n">
         <v>378.13</v>
       </c>
       <c r="F539" t="n">
-        <v>363.73</v>
+        <v>360.52</v>
       </c>
       <c r="G539" t="n">
         <v>369.74</v>
@@ -18091,6 +18091,171 @@
       <c r="I539" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="C540" t="n">
+        <v>402.19</v>
+      </c>
+      <c r="D540" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="E540" t="n">
+        <v>378.17</v>
+      </c>
+      <c r="F540" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="G540" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="H540" t="n">
+        <v>388.64</v>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="C541" t="n">
+        <v>385.78</v>
+      </c>
+      <c r="D541" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="E541" t="n">
+        <v>375.11</v>
+      </c>
+      <c r="F541" t="n">
+        <v>359.49</v>
+      </c>
+      <c r="G541" t="n">
+        <v>368.1</v>
+      </c>
+      <c r="H541" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>376.94</v>
+      </c>
+      <c r="C542" t="n">
+        <v>371.31</v>
+      </c>
+      <c r="D542" t="n">
+        <v>360.57</v>
+      </c>
+      <c r="E542" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="F542" t="n">
+        <v>358.32</v>
+      </c>
+      <c r="G542" t="n">
+        <v>366.6</v>
+      </c>
+      <c r="H542" t="n">
+        <v>385.83</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>376.94</v>
+      </c>
+      <c r="C543" t="n">
+        <v>363.98</v>
+      </c>
+      <c r="D543" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="E543" t="n">
+        <v>371.09</v>
+      </c>
+      <c r="F543" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="G543" t="n">
+        <v>364.93</v>
+      </c>
+      <c r="H543" t="n">
+        <v>384.3</v>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="C544" t="n">
+        <v>363.98</v>
+      </c>
+      <c r="D544" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="E544" t="n">
+        <v>370.43</v>
+      </c>
+      <c r="F544" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="G544" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="H544" t="n">
+        <v>383.96</v>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18105,7 +18270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23778,6 +23943,66 @@
       </c>
       <c r="B567" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -23946,28 +24171,28 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.132232600744036</v>
+        <v>-4.228011759315374</v>
       </c>
       <c r="J2" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K2" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="L2" t="n">
-        <v>0.31149250800311</v>
+        <v>0.3238119238894676</v>
       </c>
       <c r="M2" t="n">
-        <v>36.07024411946238</v>
+        <v>36.09589952324669</v>
       </c>
       <c r="N2" t="n">
-        <v>1983.8169531713</v>
+        <v>1985.13986678635</v>
       </c>
       <c r="O2" t="n">
-        <v>44.54006009393454</v>
+        <v>44.5549084477384</v>
       </c>
       <c r="P2" t="n">
-        <v>527.8814851374201</v>
+        <v>528.9340384386961</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24024,28 +24249,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.9313537107946</v>
+        <v>-4.973999905553753</v>
       </c>
       <c r="J3" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K3" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4020058288043963</v>
+        <v>0.4106362665246821</v>
       </c>
       <c r="M3" t="n">
-        <v>34.83778163451612</v>
+        <v>34.66056495258405</v>
       </c>
       <c r="N3" t="n">
-        <v>1874.535676195444</v>
+        <v>1861.633480706432</v>
       </c>
       <c r="O3" t="n">
-        <v>43.29590830777712</v>
+        <v>43.14665086314849</v>
       </c>
       <c r="P3" t="n">
-        <v>540.1051906335986</v>
+        <v>540.5810353668832</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24102,28 +24327,28 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.729801392699493</v>
+        <v>-0.7745773257083071</v>
       </c>
       <c r="J4" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K4" t="n">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04809390584138551</v>
+        <v>0.05455180872517362</v>
       </c>
       <c r="M4" t="n">
-        <v>18.68862470787009</v>
+        <v>18.69855266979378</v>
       </c>
       <c r="N4" t="n">
-        <v>559.1713940089921</v>
+        <v>558.2579039094737</v>
       </c>
       <c r="O4" t="n">
-        <v>23.64680515437534</v>
+        <v>23.62748196294886</v>
       </c>
       <c r="P4" t="n">
-        <v>410.0074032580412</v>
+        <v>410.4914772152674</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24180,28 +24405,28 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5469075508896826</v>
+        <v>-0.5449088928769132</v>
       </c>
       <c r="J5" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K5" t="n">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07552940859311885</v>
+        <v>0.07647356041976383</v>
       </c>
       <c r="M5" t="n">
-        <v>11.36553805969884</v>
+        <v>11.28450232457597</v>
       </c>
       <c r="N5" t="n">
-        <v>198.0812531806938</v>
+        <v>196.3363381652122</v>
       </c>
       <c r="O5" t="n">
-        <v>14.07413418938067</v>
+        <v>14.01200692853141</v>
       </c>
       <c r="P5" t="n">
-        <v>387.2675320446643</v>
+        <v>387.2462829264961</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24258,28 +24483,28 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4146164813013873</v>
+        <v>-0.4286684879492525</v>
       </c>
       <c r="J6" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K6" t="n">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06908898708794564</v>
+        <v>0.07469259284265617</v>
       </c>
       <c r="M6" t="n">
-        <v>9.164150135030413</v>
+        <v>9.133314186872791</v>
       </c>
       <c r="N6" t="n">
-        <v>125.53684033351</v>
+        <v>124.8515685721024</v>
       </c>
       <c r="O6" t="n">
-        <v>11.20432239510762</v>
+        <v>11.17369986048052</v>
       </c>
       <c r="P6" t="n">
-        <v>376.5748658232695</v>
+        <v>376.724593779056</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24336,28 +24561,28 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09060578617067573</v>
+        <v>-0.09990201043106466</v>
       </c>
       <c r="J7" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K7" t="n">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004223570232351537</v>
+        <v>0.005226423956998572</v>
       </c>
       <c r="M7" t="n">
-        <v>8.687008927410167</v>
+        <v>8.647090657621353</v>
       </c>
       <c r="N7" t="n">
-        <v>104.8993303297174</v>
+        <v>104.1862586275519</v>
       </c>
       <c r="O7" t="n">
-        <v>10.24203741106805</v>
+        <v>10.20716702261464</v>
       </c>
       <c r="P7" t="n">
-        <v>374.2135086062279</v>
+        <v>374.3126095220159</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24414,28 +24639,28 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03692426811648174</v>
+        <v>0.0351676996022651</v>
       </c>
       <c r="J8" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K8" t="n">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00256291573747236</v>
+        <v>0.002372191673275847</v>
       </c>
       <c r="M8" t="n">
-        <v>3.903565886777204</v>
+        <v>3.883003079346277</v>
       </c>
       <c r="N8" t="n">
-        <v>28.77096776474988</v>
+        <v>28.53776071699264</v>
       </c>
       <c r="O8" t="n">
-        <v>5.363857545158137</v>
+        <v>5.342074570519644</v>
       </c>
       <c r="P8" t="n">
-        <v>385.8469598537134</v>
+        <v>385.8657553290055</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24473,7 +24698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I539"/>
+  <dimension ref="A1:I544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49447,7 +49672,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>-36.54338105926434,174.71018812706254</t>
+          <t>-36.54333607827102,174.70993861324007</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -49494,17 +49719,17 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>-36.54338105926434,174.71018812706254</t>
+          <t>-36.54333607827102,174.70993861324007</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>-36.54399385359909,174.7094870241851</t>
+          <t>-36.54409027551008,174.71000691801973</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>-36.54465478219059,174.70914790925292</t>
+          <t>-36.544725779749136,174.70941727222166</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -49514,7 +49739,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>-36.54603721948502,174.70865276744055</t>
+          <t>-36.54602637645877,174.70861952634507</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -49530,6 +49755,241 @@
       <c r="I539" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-36.54334755446823,174.71000227248592</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-36.54409290002738,174.71002106925067</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-36.54474077954783,174.70947418144678</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-36.54543329907876,174.70917438663471</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-36.546026511574404,174.70861994056426</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-36.54671317113158,174.7084029178122</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-36.547430933124595,174.70853692658366</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-36.54334755446823,174.71000227248592</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-36.544059770418365,174.70984243723942</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-36.5447156772571,174.70937894344567</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-36.54542235433736,174.70914301447854</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-36.54602289723025,174.70860886020105</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-36.546709834590715,174.70838369882352</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-36.547429705621596,174.70851620636682</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-36.54333861325591,174.70995267495553</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-36.54403055718595,174.7096849233293</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-36.544708625094536,174.7093521876299</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-36.54541806227957,174.70913071167456</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-36.546018945095696,174.70859674429101</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-36.54670699094545,174.70836731900485</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-36.54742907866974,174.70850562346058</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-36.54333861325591,174.70995267495553</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-36.5440157586952,174.70960513228917</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-36.544695640144226,174.70930292296532</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-36.545407975938645,174.70910180009034</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-36.54601631033862,174.70858866701832</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-36.546703825017715,174.708349082808</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-36.5474280689453,174.70848857941186</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-36.54332519157257,174.70987822417715</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-36.5440157586952,174.70960513228917</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-36.54470160091064,174.70932553799258</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-36.545405615304624,174.7090950335504</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-36.54601536452825,174.70858576748466</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-36.54670331316086,174.708346134441</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-36.54742784456175,174.70848479184556</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I544"/>
+  <dimension ref="A1:I546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18137,7 +18137,7 @@
         <v>381.49</v>
       </c>
       <c r="C541" t="n">
-        <v>385.78</v>
+        <v>402.19</v>
       </c>
       <c r="D541" t="n">
         <v>363.09</v>
@@ -18170,7 +18170,7 @@
         <v>376.94</v>
       </c>
       <c r="C542" t="n">
-        <v>371.31</v>
+        <v>399.08</v>
       </c>
       <c r="D542" t="n">
         <v>360.57</v>
@@ -18203,7 +18203,7 @@
         <v>376.94</v>
       </c>
       <c r="C543" t="n">
-        <v>363.98</v>
+        <v>399.08</v>
       </c>
       <c r="D543" t="n">
         <v>355.93</v>
@@ -18236,7 +18236,7 @@
         <v>370.11</v>
       </c>
       <c r="C544" t="n">
-        <v>363.98</v>
+        <v>399.08</v>
       </c>
       <c r="D544" t="n">
         <v>358.06</v>
@@ -18256,6 +18256,72 @@
       <c r="I544" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="C545" t="n">
+        <v>399.08</v>
+      </c>
+      <c r="D545" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="E545" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="F545" t="n">
+        <v>357.13</v>
+      </c>
+      <c r="G545" t="n">
+        <v>363.83</v>
+      </c>
+      <c r="H545" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>382.58</v>
+      </c>
+      <c r="C546" t="n">
+        <v>408.32</v>
+      </c>
+      <c r="D546" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="E546" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="F546" t="n">
+        <v>354.89</v>
+      </c>
+      <c r="G546" t="n">
+        <v>361.96</v>
+      </c>
+      <c r="H546" t="n">
+        <v>380.68</v>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18270,7 +18336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24003,6 +24069,26 @@
       </c>
       <c r="B573" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
@@ -24171,28 +24257,28 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.228011759315374</v>
+        <v>-4.258481394970478</v>
       </c>
       <c r="J2" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K2" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3238119238894676</v>
+        <v>0.3281555946853565</v>
       </c>
       <c r="M2" t="n">
-        <v>36.09589952324669</v>
+        <v>36.0777730070667</v>
       </c>
       <c r="N2" t="n">
-        <v>1985.13986678635</v>
+        <v>1983.541700420644</v>
       </c>
       <c r="O2" t="n">
-        <v>44.5549084477384</v>
+        <v>44.53697004086205</v>
       </c>
       <c r="P2" t="n">
-        <v>528.9340384386961</v>
+        <v>529.2703390045425</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24249,28 +24335,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.973999905553753</v>
+        <v>-4.932079714550936</v>
       </c>
       <c r="J3" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4106362665246821</v>
+        <v>0.4099634257797244</v>
       </c>
       <c r="M3" t="n">
-        <v>34.66056495258405</v>
+        <v>34.36710311984097</v>
       </c>
       <c r="N3" t="n">
-        <v>1861.633480706432</v>
+        <v>1843.927576255923</v>
       </c>
       <c r="O3" t="n">
-        <v>43.14665086314849</v>
+        <v>42.9409778213762</v>
       </c>
       <c r="P3" t="n">
-        <v>540.5810353668832</v>
+        <v>540.1139647063178</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24327,28 +24413,28 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7745773257083071</v>
+        <v>-0.7961999602303821</v>
       </c>
       <c r="J4" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K4" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05455180872517362</v>
+        <v>0.05762868861979487</v>
       </c>
       <c r="M4" t="n">
-        <v>18.69855266979378</v>
+        <v>18.71779515549152</v>
       </c>
       <c r="N4" t="n">
-        <v>558.2579039094737</v>
+        <v>559.2054959148768</v>
       </c>
       <c r="O4" t="n">
-        <v>23.62748196294886</v>
+        <v>23.64752621131599</v>
       </c>
       <c r="P4" t="n">
-        <v>410.4914772152674</v>
+        <v>410.7259077910853</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24405,28 +24491,28 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5449088928769132</v>
+        <v>-0.5486969191332182</v>
       </c>
       <c r="J5" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K5" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07647356041976383</v>
+        <v>0.07801779694871225</v>
       </c>
       <c r="M5" t="n">
-        <v>11.28450232457597</v>
+        <v>11.26155804097381</v>
       </c>
       <c r="N5" t="n">
-        <v>196.3363381652122</v>
+        <v>195.7261330267003</v>
       </c>
       <c r="O5" t="n">
-        <v>14.01200692853141</v>
+        <v>13.99021561759147</v>
       </c>
       <c r="P5" t="n">
-        <v>387.2462829264961</v>
+        <v>387.2868386753579</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24483,28 +24569,28 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4286684879492525</v>
+        <v>-0.435549500180854</v>
       </c>
       <c r="J6" t="n">
+        <v>545</v>
+      </c>
+      <c r="K6" t="n">
         <v>543</v>
       </c>
-      <c r="K6" t="n">
-        <v>541</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.07469259284265617</v>
+        <v>0.07734023416667335</v>
       </c>
       <c r="M6" t="n">
-        <v>9.133314186872791</v>
+        <v>9.125923135779477</v>
       </c>
       <c r="N6" t="n">
-        <v>124.8515685721024</v>
+        <v>124.7063343975748</v>
       </c>
       <c r="O6" t="n">
-        <v>11.17369986048052</v>
+        <v>11.16719903993722</v>
       </c>
       <c r="P6" t="n">
-        <v>376.724593779056</v>
+        <v>376.7982040337587</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24561,28 +24647,28 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09990201043106466</v>
+        <v>-0.1064182035221655</v>
       </c>
       <c r="J7" t="n">
+        <v>545</v>
+      </c>
+      <c r="K7" t="n">
         <v>543</v>
       </c>
-      <c r="K7" t="n">
-        <v>541</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.005226423956998572</v>
+        <v>0.005959778077093358</v>
       </c>
       <c r="M7" t="n">
-        <v>8.647090657621353</v>
+        <v>8.64340733172576</v>
       </c>
       <c r="N7" t="n">
-        <v>104.1862586275519</v>
+        <v>104.083788118787</v>
       </c>
       <c r="O7" t="n">
-        <v>10.20716702261464</v>
+        <v>10.20214625060761</v>
       </c>
       <c r="P7" t="n">
-        <v>374.3126095220159</v>
+        <v>374.3823162671782</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24639,28 +24725,28 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0351676996022651</v>
+        <v>0.03140656690180803</v>
       </c>
       <c r="J8" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K8" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002372191673275847</v>
+        <v>0.001902247881243824</v>
       </c>
       <c r="M8" t="n">
-        <v>3.883003079346277</v>
+        <v>3.888017500834233</v>
       </c>
       <c r="N8" t="n">
-        <v>28.53776071699264</v>
+        <v>28.5287689904919</v>
       </c>
       <c r="O8" t="n">
-        <v>5.342074570519644</v>
+        <v>5.341232909215989</v>
       </c>
       <c r="P8" t="n">
-        <v>385.8657553290055</v>
+        <v>385.9060815215014</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24698,7 +24784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I544"/>
+  <dimension ref="A1:I546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49818,7 +49904,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>-36.544059770418365,174.70984243723942</t>
+          <t>-36.54409290002738,174.71002106925067</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -49865,7 +49951,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>-36.54403055718595,174.7096849233293</t>
+          <t>-36.5440866213716,174.70998721515352</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -49912,7 +49998,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>-36.5440157586952,174.70960513228917</t>
+          <t>-36.5440866213716,174.70998721515352</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -49959,7 +50045,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>-36.5440157586952,174.70960513228917</t>
+          <t>-36.5440866213716,174.70998721515352</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -49990,6 +50076,100 @@
       <c r="I544" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-36.54332519157257,174.70987822417715</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-36.5440866213716,174.70998721515352</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-36.54470160091064,174.70932553799258</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-36.54540332620459,174.7090884720575</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-36.546014925401984,174.70858442127263</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-36.54670173967454,174.70833707094258</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-36.54742713841276,174.70847287215162</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-36.543349696425885,174.71001415409367</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-36.54410527561291,174.7100877977594</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-36.54471911938184,174.70939200283365</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-36.54538744556282,174.70904295171093</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-36.54600735891616,174.7085612250061</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-36.5466981945883,174.70831665077276</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-36.547425679914326,174.7084482529712</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
